--- a/GA_Gruppierung_Test04.03.2026/Auswertung.xlsx
+++ b/GA_Gruppierung_Test04.03.2026/Auswertung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carey\OneDrive\Bachelorarbeit\BA-Code\GA_Gruppierung_Test10.02.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carey\OneDrive\Bachelorarbeit\BA-Code\GA_Gruppierung_Test04.03.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D5FC6C-EE80-4E82-99D5-B4D628BE18A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1369EF-9214-41E8-8ADB-20F8DD0D8964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="DOE_20260214_001909" sheetId="3" r:id="rId3"/>
     <sheet name="DOE_20260214_134754" sheetId="4" r:id="rId4"/>
     <sheet name="DOE_20260214_140559" sheetId="5" r:id="rId5"/>
+    <sheet name="DOE_20260310_222545" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,9 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="15">
   <si>
     <t>Run</t>
+  </si>
+  <si>
+    <t>Layout</t>
   </si>
   <si>
     <t>BestScore</t>
@@ -72,13 +76,13 @@
     <t>GRID_SIZE</t>
   </si>
   <si>
+    <t>Test</t>
+  </si>
+  <si>
     <t>Last Improved Gen</t>
   </si>
   <si>
-    <t>Layout</t>
-  </si>
-  <si>
-    <t>Test</t>
+    <t>Ideal_komplex</t>
   </si>
 </sst>
 </file>
@@ -413,16 +417,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -609,28 +613,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2504,34 +2508,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -11515,37 +11519,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -11553,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>279.17500000000001</v>
@@ -11591,7 +11595,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>299.14999999999998</v>
@@ -11629,7 +11633,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>295.3</v>
@@ -11667,7 +11671,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>279.05</v>
@@ -11705,7 +11709,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>292.45</v>
@@ -11743,7 +11747,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>264.60000000000002</v>
@@ -11781,7 +11785,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>303.82499999999999</v>
@@ -11819,7 +11823,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <v>366.95</v>
@@ -11857,7 +11861,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>298.32499999999999</v>
@@ -11895,7 +11899,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>288.95</v>
@@ -11933,7 +11937,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>320.7</v>
@@ -11971,7 +11975,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>313.89999999999998</v>
@@ -12009,7 +12013,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>256.52499999999998</v>
@@ -12047,7 +12051,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>230.1</v>
@@ -12085,7 +12089,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>306.12499999999989</v>
@@ -12123,7 +12127,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17">
         <v>325.3</v>
@@ -12161,7 +12165,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18">
         <v>277.2</v>
@@ -12199,7 +12203,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>321.60000000000002</v>
@@ -12237,7 +12241,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>303.85000000000002</v>
@@ -12275,7 +12279,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21">
         <v>297.14999999999998</v>
@@ -12313,7 +12317,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>251.52500000000001</v>
@@ -12351,7 +12355,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23">
         <v>264.10000000000002</v>
@@ -12389,7 +12393,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24">
         <v>294.625</v>
@@ -12427,7 +12431,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>351.55</v>
@@ -12465,7 +12469,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26">
         <v>301.27499999999998</v>
@@ -12503,7 +12507,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27">
         <v>305.85000000000002</v>
@@ -12541,7 +12545,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28">
         <v>321.35000000000002</v>
@@ -12579,7 +12583,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29">
         <v>322.7</v>
@@ -12617,7 +12621,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30">
         <v>232.65</v>
@@ -12655,7 +12659,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31">
         <v>271.10000000000002</v>
@@ -12693,7 +12697,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32">
         <v>324.52499999999998</v>
@@ -12731,7 +12735,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33">
         <v>334.8</v>
@@ -12769,7 +12773,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>274.5</v>
@@ -12807,7 +12811,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35">
         <v>278.75</v>
@@ -12845,7 +12849,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36">
         <v>328.47500000000002</v>
@@ -12883,7 +12887,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37">
         <v>293.14999999999998</v>
@@ -12921,7 +12925,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38">
         <v>272.97500000000002</v>
@@ -12959,7 +12963,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39">
         <v>281.75</v>
@@ -12997,7 +13001,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40">
         <v>284.7</v>
@@ -13035,7 +13039,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41">
         <v>292.45</v>
@@ -13073,7 +13077,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42">
         <v>274.67500000000001</v>
@@ -13111,7 +13115,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43">
         <v>290.64999999999998</v>
@@ -13149,7 +13153,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44">
         <v>302.14999999999998</v>
@@ -13187,7 +13191,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>300.50000000000011</v>
@@ -13225,7 +13229,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46">
         <v>224.05</v>
@@ -13263,7 +13267,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47">
         <v>261.75</v>
@@ -13301,7 +13305,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48">
         <v>296.7</v>
@@ -13339,7 +13343,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49">
         <v>317.85000000000002</v>
@@ -13377,7 +13381,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50">
         <v>244.25</v>
@@ -13415,7 +13419,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51">
         <v>294.30000000000013</v>
@@ -13453,7 +13457,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52">
         <v>311.8</v>
@@ -13491,7 +13495,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53">
         <v>273.84999999999991</v>
@@ -13529,7 +13533,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54">
         <v>275.22500000000002</v>
@@ -13567,7 +13571,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55">
         <v>277.64999999999998</v>
@@ -13605,7 +13609,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56">
         <v>295.14999999999998</v>
@@ -13643,7 +13647,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57">
         <v>308.3</v>
@@ -13681,7 +13685,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58">
         <v>251.65</v>
@@ -13719,7 +13723,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59">
         <v>300.5</v>
@@ -13757,7 +13761,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60">
         <v>279.82499999999999</v>
@@ -13795,7 +13799,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61">
         <v>313.95</v>
@@ -13833,7 +13837,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62">
         <v>230.07499999999999</v>
@@ -13871,7 +13875,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63">
         <v>295.25</v>
@@ -13909,7 +13913,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64">
         <v>294.14999999999998</v>
@@ -13947,7 +13951,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65">
         <v>318.75000000000011</v>
@@ -13985,7 +13989,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66">
         <v>271.05</v>
@@ -14023,7 +14027,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67">
         <v>285.64999999999998</v>
@@ -14061,7 +14065,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68">
         <v>314.60000000000002</v>
@@ -14099,7 +14103,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69">
         <v>310.5</v>
@@ -14137,7 +14141,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70">
         <v>251.57499999999999</v>
@@ -14175,7 +14179,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71">
         <v>308.95</v>
@@ -14213,7 +14217,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72">
         <v>293.3</v>
@@ -14251,7 +14255,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73">
         <v>309.5</v>
@@ -14289,7 +14293,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74">
         <v>315.375</v>
@@ -14327,7 +14331,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75">
         <v>363.25</v>
@@ -14365,7 +14369,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76">
         <v>293.27499999999998</v>
@@ -14403,7 +14407,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77">
         <v>332.6</v>
@@ -14441,7 +14445,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78">
         <v>253.45</v>
@@ -14479,7 +14483,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79">
         <v>275.10000000000002</v>
@@ -14517,7 +14521,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80">
         <v>315.47500000000002</v>
@@ -14555,7 +14559,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81">
         <v>310.8</v>
@@ -14593,7 +14597,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82">
         <v>304.05</v>
@@ -14631,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83">
         <v>304.39999999999998</v>
@@ -14669,7 +14673,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C84">
         <v>295.25000000000011</v>
@@ -14707,7 +14711,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85">
         <v>319.60000000000002</v>
@@ -14745,7 +14749,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86">
         <v>253.95</v>
@@ -14783,7 +14787,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87">
         <v>283.5</v>
@@ -14821,7 +14825,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C88">
         <v>289.72500000000002</v>
@@ -14859,7 +14863,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89">
         <v>344.05</v>
@@ -14897,7 +14901,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C90">
         <v>304.97500000000002</v>
@@ -14935,7 +14939,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C91">
         <v>270.85000000000002</v>
@@ -14973,7 +14977,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C92">
         <v>308.42500000000001</v>
@@ -15011,7 +15015,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93">
         <v>293.24999999999989</v>
@@ -15049,7 +15053,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94">
         <v>277.05</v>
@@ -15087,7 +15091,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95">
         <v>302.64999999999998</v>
@@ -15125,7 +15129,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C96">
         <v>294.39999999999992</v>
@@ -15163,7 +15167,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C97">
         <v>295.25</v>
@@ -15201,7 +15205,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C98">
         <v>245.375</v>
@@ -15239,7 +15243,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C99">
         <v>268.95</v>
@@ -15277,7 +15281,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C100">
         <v>274.52499999999998</v>
@@ -15315,7 +15319,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C101">
         <v>284</v>
@@ -15353,7 +15357,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C102">
         <v>228.27500000000001</v>
@@ -15391,7 +15395,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C103">
         <v>227.35</v>
@@ -15429,7 +15433,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C104">
         <v>317</v>
@@ -15467,7 +15471,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C105">
         <v>316.34999999999991</v>
@@ -15505,7 +15509,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C106">
         <v>250.875</v>
@@ -15543,7 +15547,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107">
         <v>276.89999999999998</v>
@@ -15581,7 +15585,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C108">
         <v>274</v>
@@ -15619,7 +15623,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109">
         <v>280</v>
@@ -15657,7 +15661,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C110">
         <v>233</v>
@@ -15695,7 +15699,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C111">
         <v>223.1</v>
@@ -15733,7 +15737,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C112">
         <v>279.77499999999998</v>
@@ -15771,7 +15775,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113">
         <v>336.65</v>
@@ -15809,7 +15813,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C114">
         <v>268.89999999999998</v>
@@ -15847,7 +15851,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C115">
         <v>283.95</v>
@@ -15885,7 +15889,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C116">
         <v>239.92500000000001</v>
@@ -15923,7 +15927,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117">
         <v>293.05</v>
@@ -15961,7 +15965,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C118">
         <v>230.97499999999999</v>
@@ -15999,7 +16003,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C119">
         <v>277.10000000000002</v>
@@ -16037,7 +16041,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C120">
         <v>245.77500000000001</v>
@@ -16075,7 +16079,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C121">
         <v>313.64999999999998</v>
@@ -16113,7 +16117,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122">
         <v>246.27500000000001</v>
@@ -16151,7 +16155,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C123">
         <v>252.9</v>
@@ -16189,7 +16193,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C124">
         <v>267.22500000000002</v>
@@ -16227,7 +16231,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C125">
         <v>303.39999999999998</v>
@@ -16265,7 +16269,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C126">
         <v>263.375</v>
@@ -16303,7 +16307,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C127">
         <v>252</v>
@@ -16341,7 +16345,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C128">
         <v>268.5</v>
@@ -16379,7 +16383,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C129">
         <v>335.64999999999992</v>
@@ -16417,7 +16421,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C130">
         <v>276.5</v>
@@ -16455,7 +16459,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C131">
         <v>282.2</v>
@@ -16493,7 +16497,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C132">
         <v>287.75</v>
@@ -16531,7 +16535,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C133">
         <v>280.05</v>
@@ -16569,7 +16573,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C134">
         <v>231.47499999999999</v>
@@ -16607,7 +16611,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135">
         <v>264</v>
@@ -16645,7 +16649,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C136">
         <v>265.60000000000002</v>
@@ -16683,7 +16687,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C137">
         <v>285.35000000000002</v>
@@ -16721,7 +16725,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138">
         <v>270.14999999999998</v>
@@ -16759,7 +16763,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C139">
         <v>301.75000000000011</v>
@@ -16797,7 +16801,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C140">
         <v>253.55</v>
@@ -16835,7 +16839,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C141">
         <v>296.64999999999998</v>
@@ -16873,7 +16877,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C142">
         <v>247.625</v>
@@ -16911,7 +16915,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C143">
         <v>263.39999999999998</v>
@@ -16949,7 +16953,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C144">
         <v>282.5</v>
@@ -16987,7 +16991,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C145">
         <v>281.8</v>
@@ -17025,7 +17029,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C146">
         <v>277.85000000000002</v>
@@ -17063,7 +17067,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C147">
         <v>261.35000000000002</v>
@@ -17101,7 +17105,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C148">
         <v>301.97500000000002</v>
@@ -17139,7 +17143,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C149">
         <v>297.39999999999998</v>
@@ -17177,7 +17181,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C150">
         <v>230.47499999999999</v>
@@ -17215,7 +17219,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C151">
         <v>250.3</v>
@@ -17253,7 +17257,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C152">
         <v>281.77499999999998</v>
@@ -17291,7 +17295,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C153">
         <v>288.00000000000011</v>
@@ -17329,7 +17333,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C154">
         <v>252.75</v>
@@ -17367,7 +17371,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C155">
         <v>290.7</v>
@@ -17405,7 +17409,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C156">
         <v>289.47500000000002</v>
@@ -17443,7 +17447,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C157">
         <v>300.39999999999992</v>
@@ -17481,7 +17485,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C158">
         <v>230.85</v>
@@ -17519,7 +17523,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C159">
         <v>266.39999999999998</v>
@@ -17557,7 +17561,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C160">
         <v>306.05</v>
@@ -17595,7 +17599,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C161">
         <v>279.60000000000002</v>
@@ -17633,7 +17637,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C162">
         <v>258.7</v>
@@ -17671,7 +17675,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C163">
         <v>282.2</v>
@@ -17709,7 +17713,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C164">
         <v>296.12499999999989</v>
@@ -17747,7 +17751,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C165">
         <v>299.45</v>
@@ -17785,7 +17789,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C166">
         <v>232.75</v>
@@ -17823,7 +17827,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C167">
         <v>279.64999999999998</v>
@@ -17861,7 +17865,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C168">
         <v>298.22500000000002</v>
@@ -17899,7 +17903,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C169">
         <v>315.10000000000002</v>
@@ -17937,7 +17941,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C170">
         <v>246.65</v>
@@ -17975,7 +17979,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C171">
         <v>259.5</v>
@@ -18013,7 +18017,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C172">
         <v>247</v>
@@ -18051,7 +18055,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C173">
         <v>286.75</v>
@@ -18089,7 +18093,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C174">
         <v>228.4</v>
@@ -18127,7 +18131,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C175">
         <v>240</v>
@@ -18165,7 +18169,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C176">
         <v>247.375</v>
@@ -18203,7 +18207,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C177">
         <v>290.89999999999998</v>
@@ -18241,7 +18245,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C178">
         <v>228</v>
@@ -18279,7 +18283,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C179">
         <v>263.2</v>
@@ -18317,7 +18321,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C180">
         <v>268.60000000000002</v>
@@ -18355,7 +18359,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C181">
         <v>280.3</v>
@@ -18393,7 +18397,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C182">
         <v>214.17500000000001</v>
@@ -18431,7 +18435,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C183">
         <v>271.94999999999987</v>
@@ -18469,7 +18473,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C184">
         <v>302.14999999999998</v>
@@ -18507,7 +18511,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C185">
         <v>293.2</v>
@@ -18545,7 +18549,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C186">
         <v>241.625</v>
@@ -18583,7 +18587,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C187">
         <v>271.64999999999998</v>
@@ -18621,7 +18625,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C188">
         <v>286.07499999999987</v>
@@ -18659,7 +18663,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C189">
         <v>291.99999999999989</v>
@@ -18697,7 +18701,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C190">
         <v>220.6</v>
@@ -18735,7 +18739,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C191">
         <v>243.1</v>
@@ -18773,7 +18777,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C192">
         <v>294.77499999999998</v>
@@ -18811,7 +18815,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C193">
         <v>289.74999999999989</v>
@@ -18849,7 +18853,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C194">
         <v>268.35000000000002</v>
@@ -18887,7 +18891,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C195">
         <v>291.35000000000002</v>
@@ -18925,7 +18929,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C196">
         <v>254.375</v>
@@ -18963,7 +18967,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C197">
         <v>306.3</v>
@@ -19001,7 +19005,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C198">
         <v>231.02500000000001</v>
@@ -19039,7 +19043,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C199">
         <v>260.95</v>
@@ -19077,7 +19081,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C200">
         <v>287.52499999999998</v>
@@ -19115,7 +19119,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C201">
         <v>286.74999999999989</v>
@@ -19153,7 +19157,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C202">
         <v>266.25</v>
@@ -19191,7 +19195,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C203">
         <v>305.5</v>
@@ -19229,7 +19233,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C204">
         <v>315.92500000000001</v>
@@ -19267,7 +19271,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C205">
         <v>289.2</v>
@@ -19305,7 +19309,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C206">
         <v>249.35</v>
@@ -19343,7 +19347,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C207">
         <v>279.45</v>
@@ -19381,7 +19385,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C208">
         <v>274.75000000000011</v>
@@ -19419,7 +19423,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C209">
         <v>313.55</v>
@@ -19457,7 +19461,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C210">
         <v>250.375</v>
@@ -19495,7 +19499,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C211">
         <v>309.89999999999998</v>
@@ -19533,7 +19537,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C212">
         <v>260.22500000000002</v>
@@ -19571,7 +19575,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C213">
         <v>279.2</v>
@@ -19609,7 +19613,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C214">
         <v>250.375</v>
@@ -19647,7 +19651,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C215">
         <v>255.9</v>
@@ -19685,7 +19689,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C216">
         <v>288.25000000000011</v>
@@ -19723,7 +19727,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C217">
         <v>299.80000000000013</v>
@@ -19761,7 +19765,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C218">
         <v>280.02499999999998</v>
@@ -19799,7 +19803,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C219">
         <v>255.95</v>
@@ -19837,7 +19841,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C220">
         <v>289.67500000000001</v>
@@ -19875,7 +19879,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C221">
         <v>318.3</v>
@@ -19913,7 +19917,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C222">
         <v>252.42500000000001</v>
@@ -19951,7 +19955,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C223">
         <v>262.05</v>
@@ -19989,7 +19993,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C224">
         <v>299.10000000000002</v>
@@ -20027,7 +20031,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C225">
         <v>296.60000000000002</v>
@@ -20065,7 +20069,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C226">
         <v>216.7</v>
@@ -20103,7 +20107,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C227">
         <v>234</v>
@@ -20141,7 +20145,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C228">
         <v>282.02499999999998</v>
@@ -20179,7 +20183,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C229">
         <v>271</v>
@@ -20217,7 +20221,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C230">
         <v>243.625</v>
@@ -20255,7 +20259,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C231">
         <v>228.8</v>
@@ -20293,7 +20297,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C232">
         <v>283.57499999999999</v>
@@ -20331,7 +20335,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C233">
         <v>304.89999999999992</v>
@@ -20369,7 +20373,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C234">
         <v>254.07499999999999</v>
@@ -20407,7 +20411,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C235">
         <v>241.7</v>
@@ -20445,7 +20449,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C236">
         <v>268.05</v>
@@ -20483,7 +20487,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C237">
         <v>277.64999999999998</v>
@@ -20521,7 +20525,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C238">
         <v>214.5</v>
@@ -20559,7 +20563,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C239">
         <v>213.15</v>
@@ -20597,7 +20601,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C240">
         <v>256.35000000000002</v>
@@ -20635,7 +20639,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C241">
         <v>264</v>
@@ -20673,7 +20677,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C242">
         <v>236.3</v>
@@ -20711,7 +20715,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C243">
         <v>232.8</v>
@@ -20749,7 +20753,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C244">
         <v>266.32499999999999</v>
@@ -20787,7 +20791,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C245">
         <v>274.60000000000002</v>
@@ -20825,7 +20829,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C246">
         <v>238.67500000000001</v>
@@ -20863,7 +20867,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C247">
         <v>257.2</v>
@@ -20901,7 +20905,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C248">
         <v>298.64999999999998</v>
@@ -20939,7 +20943,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C249">
         <v>275.14999999999998</v>
@@ -20977,7 +20981,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C250">
         <v>236.8</v>
@@ -21015,7 +21019,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C251">
         <v>234.7</v>
@@ -21053,7 +21057,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C252">
         <v>272.8</v>
@@ -21091,7 +21095,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C253">
         <v>261</v>
@@ -21129,7 +21133,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C254">
         <v>188.375</v>
@@ -21167,7 +21171,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C255">
         <v>219.95</v>
@@ -21205,7 +21209,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C256">
         <v>279.60000000000002</v>
@@ -21243,7 +21247,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C257">
         <v>303.95</v>
@@ -21285,4 +21289,5931 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G258"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>99.6</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>0.1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>104.8</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>112.8</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>93.799999999999983</v>
+      </c>
+      <c r="D5">
+        <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>0.1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>115.1</v>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6">
+        <v>0.1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>132</v>
+      </c>
+      <c r="D7">
+        <v>0.1</v>
+      </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>126.8</v>
+      </c>
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8">
+        <v>0.1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.1</v>
+      </c>
+      <c r="E9">
+        <v>0.1</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>117.8</v>
+      </c>
+      <c r="D10">
+        <v>0.1</v>
+      </c>
+      <c r="E10">
+        <v>0.1</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>0.1</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="D12">
+        <v>0.1</v>
+      </c>
+      <c r="E12">
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>147.6</v>
+      </c>
+      <c r="D13">
+        <v>0.1</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="D14">
+        <v>0.1</v>
+      </c>
+      <c r="E14">
+        <v>0.1</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>131.5</v>
+      </c>
+      <c r="D15">
+        <v>0.1</v>
+      </c>
+      <c r="E15">
+        <v>0.1</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>157.5</v>
+      </c>
+      <c r="D16">
+        <v>0.1</v>
+      </c>
+      <c r="E16">
+        <v>0.1</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>132.6</v>
+      </c>
+      <c r="D17">
+        <v>0.1</v>
+      </c>
+      <c r="E17">
+        <v>0.1</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>126.3</v>
+      </c>
+      <c r="D18">
+        <v>0.1</v>
+      </c>
+      <c r="E18">
+        <v>0.2</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D19">
+        <v>0.1</v>
+      </c>
+      <c r="E19">
+        <v>0.2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>138.6</v>
+      </c>
+      <c r="D20">
+        <v>0.1</v>
+      </c>
+      <c r="E20">
+        <v>0.2</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="D21">
+        <v>0.1</v>
+      </c>
+      <c r="E21">
+        <v>0.2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="D22">
+        <v>0.1</v>
+      </c>
+      <c r="E22">
+        <v>0.2</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="D23">
+        <v>0.1</v>
+      </c>
+      <c r="E23">
+        <v>0.2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>140.5</v>
+      </c>
+      <c r="D24">
+        <v>0.1</v>
+      </c>
+      <c r="E24">
+        <v>0.2</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="D25">
+        <v>0.1</v>
+      </c>
+      <c r="E25">
+        <v>0.2</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>133.30000000000001</v>
+      </c>
+      <c r="D26">
+        <v>0.1</v>
+      </c>
+      <c r="E26">
+        <v>0.2</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>143</v>
+      </c>
+      <c r="D27">
+        <v>0.1</v>
+      </c>
+      <c r="E27">
+        <v>0.2</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="D28">
+        <v>0.1</v>
+      </c>
+      <c r="E28">
+        <v>0.2</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>138.1</v>
+      </c>
+      <c r="D29">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>0.2</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>134.4</v>
+      </c>
+      <c r="D30">
+        <v>0.1</v>
+      </c>
+      <c r="E30">
+        <v>0.2</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="D31">
+        <v>0.1</v>
+      </c>
+      <c r="E31">
+        <v>0.2</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>136.69999999999999</v>
+      </c>
+      <c r="D32">
+        <v>0.1</v>
+      </c>
+      <c r="E32">
+        <v>0.2</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="D33">
+        <v>0.1</v>
+      </c>
+      <c r="E33">
+        <v>0.2</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>151.5</v>
+      </c>
+      <c r="D34">
+        <v>0.1</v>
+      </c>
+      <c r="E34">
+        <v>0.3</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>135.69999999999999</v>
+      </c>
+      <c r="D35">
+        <v>0.1</v>
+      </c>
+      <c r="E35">
+        <v>0.3</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>138.5</v>
+      </c>
+      <c r="D36">
+        <v>0.1</v>
+      </c>
+      <c r="E36">
+        <v>0.3</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37">
+        <v>136.1</v>
+      </c>
+      <c r="D37">
+        <v>0.1</v>
+      </c>
+      <c r="E37">
+        <v>0.3</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38">
+        <v>146</v>
+      </c>
+      <c r="D38">
+        <v>0.1</v>
+      </c>
+      <c r="E38">
+        <v>0.3</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39">
+        <v>157.1</v>
+      </c>
+      <c r="D39">
+        <v>0.1</v>
+      </c>
+      <c r="E39">
+        <v>0.3</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40">
+        <v>148.5</v>
+      </c>
+      <c r="D40">
+        <v>0.1</v>
+      </c>
+      <c r="E40">
+        <v>0.3</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="D41">
+        <v>0.1</v>
+      </c>
+      <c r="E41">
+        <v>0.3</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42">
+        <v>154</v>
+      </c>
+      <c r="D42">
+        <v>0.1</v>
+      </c>
+      <c r="E42">
+        <v>0.3</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>151.1</v>
+      </c>
+      <c r="D43">
+        <v>0.1</v>
+      </c>
+      <c r="E43">
+        <v>0.3</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44">
+        <v>125.8</v>
+      </c>
+      <c r="D44">
+        <v>0.1</v>
+      </c>
+      <c r="E44">
+        <v>0.3</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>147.5</v>
+      </c>
+      <c r="D45">
+        <v>0.1</v>
+      </c>
+      <c r="E45">
+        <v>0.3</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46">
+        <v>136.30000000000001</v>
+      </c>
+      <c r="D46">
+        <v>0.1</v>
+      </c>
+      <c r="E46">
+        <v>0.3</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="D47">
+        <v>0.1</v>
+      </c>
+      <c r="E47">
+        <v>0.3</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="D48">
+        <v>0.1</v>
+      </c>
+      <c r="E48">
+        <v>0.3</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="D49">
+        <v>0.1</v>
+      </c>
+      <c r="E49">
+        <v>0.3</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="D50">
+        <v>0.1</v>
+      </c>
+      <c r="E50">
+        <v>0.4</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>148.1</v>
+      </c>
+      <c r="D51">
+        <v>0.1</v>
+      </c>
+      <c r="E51">
+        <v>0.4</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52">
+        <v>122.8</v>
+      </c>
+      <c r="D52">
+        <v>0.1</v>
+      </c>
+      <c r="E52">
+        <v>0.4</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>142.5</v>
+      </c>
+      <c r="D53">
+        <v>0.1</v>
+      </c>
+      <c r="E53">
+        <v>0.4</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>117.8</v>
+      </c>
+      <c r="D54">
+        <v>0.1</v>
+      </c>
+      <c r="E54">
+        <v>0.4</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55">
+        <v>143.6</v>
+      </c>
+      <c r="D55">
+        <v>0.1</v>
+      </c>
+      <c r="E55">
+        <v>0.4</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56">
+        <v>135.6</v>
+      </c>
+      <c r="D56">
+        <v>0.1</v>
+      </c>
+      <c r="E56">
+        <v>0.4</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57">
+        <v>150</v>
+      </c>
+      <c r="D57">
+        <v>0.1</v>
+      </c>
+      <c r="E57">
+        <v>0.4</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="D58">
+        <v>0.1</v>
+      </c>
+      <c r="E58">
+        <v>0.4</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="D59">
+        <v>0.1</v>
+      </c>
+      <c r="E59">
+        <v>0.4</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="D60">
+        <v>0.1</v>
+      </c>
+      <c r="E60">
+        <v>0.4</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="D61">
+        <v>0.1</v>
+      </c>
+      <c r="E61">
+        <v>0.4</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62">
+        <v>130.80000000000001</v>
+      </c>
+      <c r="D62">
+        <v>0.1</v>
+      </c>
+      <c r="E62">
+        <v>0.4</v>
+      </c>
+      <c r="F62">
+        <v>4</v>
+      </c>
+      <c r="G62">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="D63">
+        <v>0.1</v>
+      </c>
+      <c r="E63">
+        <v>0.4</v>
+      </c>
+      <c r="F63">
+        <v>4</v>
+      </c>
+      <c r="G63">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="D64">
+        <v>0.1</v>
+      </c>
+      <c r="E64">
+        <v>0.4</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="D65">
+        <v>0.1</v>
+      </c>
+      <c r="E65">
+        <v>0.4</v>
+      </c>
+      <c r="F65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>133.30000000000001</v>
+      </c>
+      <c r="D66">
+        <v>0.2</v>
+      </c>
+      <c r="E66">
+        <v>0.1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="D67">
+        <v>0.2</v>
+      </c>
+      <c r="E67">
+        <v>0.1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68">
+        <v>152.1</v>
+      </c>
+      <c r="D68">
+        <v>0.2</v>
+      </c>
+      <c r="E68">
+        <v>0.1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="D69">
+        <v>0.2</v>
+      </c>
+      <c r="E69">
+        <v>0.1</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="D70">
+        <v>0.2</v>
+      </c>
+      <c r="E70">
+        <v>0.1</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71">
+        <v>133.6</v>
+      </c>
+      <c r="D71">
+        <v>0.2</v>
+      </c>
+      <c r="E71">
+        <v>0.1</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="D72">
+        <v>0.2</v>
+      </c>
+      <c r="E72">
+        <v>0.1</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>160</v>
+      </c>
+      <c r="D73">
+        <v>0.2</v>
+      </c>
+      <c r="E73">
+        <v>0.1</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="D74">
+        <v>0.2</v>
+      </c>
+      <c r="E74">
+        <v>0.1</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="D75">
+        <v>0.2</v>
+      </c>
+      <c r="E75">
+        <v>0.1</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="D76">
+        <v>0.2</v>
+      </c>
+      <c r="E76">
+        <v>0.1</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77">
+        <v>159.80000000000001</v>
+      </c>
+      <c r="D77">
+        <v>0.2</v>
+      </c>
+      <c r="E77">
+        <v>0.1</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="D78">
+        <v>0.2</v>
+      </c>
+      <c r="E78">
+        <v>0.1</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79">
+        <v>150.1</v>
+      </c>
+      <c r="D79">
+        <v>0.2</v>
+      </c>
+      <c r="E79">
+        <v>0.1</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+      <c r="G79">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80">
+        <v>146.5</v>
+      </c>
+      <c r="D80">
+        <v>0.2</v>
+      </c>
+      <c r="E80">
+        <v>0.1</v>
+      </c>
+      <c r="F80">
+        <v>4</v>
+      </c>
+      <c r="G80">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="D81">
+        <v>0.2</v>
+      </c>
+      <c r="E81">
+        <v>0.1</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+      <c r="G81">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82">
+        <v>152.1</v>
+      </c>
+      <c r="D82">
+        <v>0.2</v>
+      </c>
+      <c r="E82">
+        <v>0.2</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83">
+        <v>125.6</v>
+      </c>
+      <c r="D83">
+        <v>0.2</v>
+      </c>
+      <c r="E83">
+        <v>0.2</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D84">
+        <v>0.2</v>
+      </c>
+      <c r="E84">
+        <v>0.2</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D85">
+        <v>0.2</v>
+      </c>
+      <c r="E85">
+        <v>0.2</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="D86">
+        <v>0.2</v>
+      </c>
+      <c r="E86">
+        <v>0.2</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87">
+        <v>142</v>
+      </c>
+      <c r="D87">
+        <v>0.2</v>
+      </c>
+      <c r="E87">
+        <v>0.2</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88">
+        <v>132.5</v>
+      </c>
+      <c r="D88">
+        <v>0.2</v>
+      </c>
+      <c r="E88">
+        <v>0.2</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="D89">
+        <v>0.2</v>
+      </c>
+      <c r="E89">
+        <v>0.2</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="D90">
+        <v>0.2</v>
+      </c>
+      <c r="E90">
+        <v>0.2</v>
+      </c>
+      <c r="F90">
+        <v>3</v>
+      </c>
+      <c r="G90">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91">
+        <v>132.5</v>
+      </c>
+      <c r="D91">
+        <v>0.2</v>
+      </c>
+      <c r="E91">
+        <v>0.2</v>
+      </c>
+      <c r="F91">
+        <v>3</v>
+      </c>
+      <c r="G91">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="D92">
+        <v>0.2</v>
+      </c>
+      <c r="E92">
+        <v>0.2</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="G92">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93">
+        <v>153.1</v>
+      </c>
+      <c r="D93">
+        <v>0.2</v>
+      </c>
+      <c r="E93">
+        <v>0.2</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D94">
+        <v>0.2</v>
+      </c>
+      <c r="E94">
+        <v>0.2</v>
+      </c>
+      <c r="F94">
+        <v>4</v>
+      </c>
+      <c r="G94">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95">
+        <v>142.6</v>
+      </c>
+      <c r="D95">
+        <v>0.2</v>
+      </c>
+      <c r="E95">
+        <v>0.2</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D96">
+        <v>0.2</v>
+      </c>
+      <c r="E96">
+        <v>0.2</v>
+      </c>
+      <c r="F96">
+        <v>4</v>
+      </c>
+      <c r="G96">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97">
+        <v>146</v>
+      </c>
+      <c r="D97">
+        <v>0.2</v>
+      </c>
+      <c r="E97">
+        <v>0.2</v>
+      </c>
+      <c r="F97">
+        <v>4</v>
+      </c>
+      <c r="G97">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="D98">
+        <v>0.2</v>
+      </c>
+      <c r="E98">
+        <v>0.3</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="D99">
+        <v>0.2</v>
+      </c>
+      <c r="E99">
+        <v>0.3</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="D100">
+        <v>0.2</v>
+      </c>
+      <c r="E100">
+        <v>0.3</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101">
+        <v>134.80000000000001</v>
+      </c>
+      <c r="D101">
+        <v>0.2</v>
+      </c>
+      <c r="E101">
+        <v>0.3</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102">
+        <v>151</v>
+      </c>
+      <c r="D102">
+        <v>0.2</v>
+      </c>
+      <c r="E102">
+        <v>0.3</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="G102">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103">
+        <v>144.30000000000001</v>
+      </c>
+      <c r="D103">
+        <v>0.2</v>
+      </c>
+      <c r="E103">
+        <v>0.3</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="G103">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="D104">
+        <v>0.2</v>
+      </c>
+      <c r="E104">
+        <v>0.3</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105">
+        <v>143</v>
+      </c>
+      <c r="D105">
+        <v>0.2</v>
+      </c>
+      <c r="E105">
+        <v>0.3</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+      <c r="G105">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="D106">
+        <v>0.2</v>
+      </c>
+      <c r="E106">
+        <v>0.3</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="D107">
+        <v>0.2</v>
+      </c>
+      <c r="E107">
+        <v>0.3</v>
+      </c>
+      <c r="F107">
+        <v>3</v>
+      </c>
+      <c r="G107">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="D108">
+        <v>0.2</v>
+      </c>
+      <c r="E108">
+        <v>0.3</v>
+      </c>
+      <c r="F108">
+        <v>3</v>
+      </c>
+      <c r="G108">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109">
+        <v>149.6</v>
+      </c>
+      <c r="D109">
+        <v>0.2</v>
+      </c>
+      <c r="E109">
+        <v>0.3</v>
+      </c>
+      <c r="F109">
+        <v>3</v>
+      </c>
+      <c r="G109">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110">
+        <v>149.1</v>
+      </c>
+      <c r="D110">
+        <v>0.2</v>
+      </c>
+      <c r="E110">
+        <v>0.3</v>
+      </c>
+      <c r="F110">
+        <v>4</v>
+      </c>
+      <c r="G110">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="D111">
+        <v>0.2</v>
+      </c>
+      <c r="E111">
+        <v>0.3</v>
+      </c>
+      <c r="F111">
+        <v>4</v>
+      </c>
+      <c r="G111">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="D112">
+        <v>0.2</v>
+      </c>
+      <c r="E112">
+        <v>0.3</v>
+      </c>
+      <c r="F112">
+        <v>4</v>
+      </c>
+      <c r="G112">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113">
+        <v>149.5</v>
+      </c>
+      <c r="D113">
+        <v>0.2</v>
+      </c>
+      <c r="E113">
+        <v>0.3</v>
+      </c>
+      <c r="F113">
+        <v>4</v>
+      </c>
+      <c r="G113">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114">
+        <v>149.6</v>
+      </c>
+      <c r="D114">
+        <v>0.2</v>
+      </c>
+      <c r="E114">
+        <v>0.4</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115">
+        <v>144.30000000000001</v>
+      </c>
+      <c r="D115">
+        <v>0.2</v>
+      </c>
+      <c r="E115">
+        <v>0.4</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116">
+        <v>144.5</v>
+      </c>
+      <c r="D116">
+        <v>0.2</v>
+      </c>
+      <c r="E116">
+        <v>0.4</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117">
+        <v>160</v>
+      </c>
+      <c r="D117">
+        <v>0.2</v>
+      </c>
+      <c r="E117">
+        <v>0.4</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="D118">
+        <v>0.2</v>
+      </c>
+      <c r="E118">
+        <v>0.4</v>
+      </c>
+      <c r="F118">
+        <v>2</v>
+      </c>
+      <c r="G118">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D119">
+        <v>0.2</v>
+      </c>
+      <c r="E119">
+        <v>0.4</v>
+      </c>
+      <c r="F119">
+        <v>2</v>
+      </c>
+      <c r="G119">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120">
+        <v>115.5</v>
+      </c>
+      <c r="D120">
+        <v>0.2</v>
+      </c>
+      <c r="E120">
+        <v>0.4</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121">
+        <v>150.1</v>
+      </c>
+      <c r="D121">
+        <v>0.2</v>
+      </c>
+      <c r="E121">
+        <v>0.4</v>
+      </c>
+      <c r="F121">
+        <v>2</v>
+      </c>
+      <c r="G121">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122">
+        <v>115.3</v>
+      </c>
+      <c r="D122">
+        <v>0.2</v>
+      </c>
+      <c r="E122">
+        <v>0.4</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123">
+        <v>139</v>
+      </c>
+      <c r="D123">
+        <v>0.2</v>
+      </c>
+      <c r="E123">
+        <v>0.4</v>
+      </c>
+      <c r="F123">
+        <v>3</v>
+      </c>
+      <c r="G123">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="D124">
+        <v>0.2</v>
+      </c>
+      <c r="E124">
+        <v>0.4</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125">
+        <v>136.30000000000001</v>
+      </c>
+      <c r="D125">
+        <v>0.2</v>
+      </c>
+      <c r="E125">
+        <v>0.4</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126">
+        <v>148</v>
+      </c>
+      <c r="D126">
+        <v>0.2</v>
+      </c>
+      <c r="E126">
+        <v>0.4</v>
+      </c>
+      <c r="F126">
+        <v>4</v>
+      </c>
+      <c r="G126">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="D127">
+        <v>0.2</v>
+      </c>
+      <c r="E127">
+        <v>0.4</v>
+      </c>
+      <c r="F127">
+        <v>4</v>
+      </c>
+      <c r="G127">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="D128">
+        <v>0.2</v>
+      </c>
+      <c r="E128">
+        <v>0.4</v>
+      </c>
+      <c r="F128">
+        <v>4</v>
+      </c>
+      <c r="G128">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129">
+        <v>147.1</v>
+      </c>
+      <c r="D129">
+        <v>0.2</v>
+      </c>
+      <c r="E129">
+        <v>0.4</v>
+      </c>
+      <c r="F129">
+        <v>4</v>
+      </c>
+      <c r="G129">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130">
+        <v>138</v>
+      </c>
+      <c r="D130">
+        <v>0.3</v>
+      </c>
+      <c r="E130">
+        <v>0.1</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D131">
+        <v>0.3</v>
+      </c>
+      <c r="E131">
+        <v>0.1</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="D132">
+        <v>0.3</v>
+      </c>
+      <c r="E132">
+        <v>0.1</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133">
+        <v>151.6</v>
+      </c>
+      <c r="D133">
+        <v>0.3</v>
+      </c>
+      <c r="E133">
+        <v>0.1</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134">
+        <v>142.4</v>
+      </c>
+      <c r="D134">
+        <v>0.3</v>
+      </c>
+      <c r="E134">
+        <v>0.1</v>
+      </c>
+      <c r="F134">
+        <v>2</v>
+      </c>
+      <c r="G134">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135">
+        <v>142.1</v>
+      </c>
+      <c r="D135">
+        <v>0.3</v>
+      </c>
+      <c r="E135">
+        <v>0.1</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+      <c r="G135">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136">
+        <v>159.5</v>
+      </c>
+      <c r="D136">
+        <v>0.3</v>
+      </c>
+      <c r="E136">
+        <v>0.1</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="D137">
+        <v>0.3</v>
+      </c>
+      <c r="E137">
+        <v>0.1</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="D138">
+        <v>0.3</v>
+      </c>
+      <c r="E138">
+        <v>0.1</v>
+      </c>
+      <c r="F138">
+        <v>3</v>
+      </c>
+      <c r="G138">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="D139">
+        <v>0.3</v>
+      </c>
+      <c r="E139">
+        <v>0.1</v>
+      </c>
+      <c r="F139">
+        <v>3</v>
+      </c>
+      <c r="G139">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="D140">
+        <v>0.3</v>
+      </c>
+      <c r="E140">
+        <v>0.1</v>
+      </c>
+      <c r="F140">
+        <v>3</v>
+      </c>
+      <c r="G140">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141">
+        <v>147.6</v>
+      </c>
+      <c r="D141">
+        <v>0.3</v>
+      </c>
+      <c r="E141">
+        <v>0.1</v>
+      </c>
+      <c r="F141">
+        <v>3</v>
+      </c>
+      <c r="G141">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142">
+        <v>150.5</v>
+      </c>
+      <c r="D142">
+        <v>0.3</v>
+      </c>
+      <c r="E142">
+        <v>0.1</v>
+      </c>
+      <c r="F142">
+        <v>4</v>
+      </c>
+      <c r="G142">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="D143">
+        <v>0.3</v>
+      </c>
+      <c r="E143">
+        <v>0.1</v>
+      </c>
+      <c r="F143">
+        <v>4</v>
+      </c>
+      <c r="G143">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D144">
+        <v>0.3</v>
+      </c>
+      <c r="E144">
+        <v>0.1</v>
+      </c>
+      <c r="F144">
+        <v>4</v>
+      </c>
+      <c r="G144">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>14</v>
+      </c>
+      <c r="C145">
+        <v>142.6</v>
+      </c>
+      <c r="D145">
+        <v>0.3</v>
+      </c>
+      <c r="E145">
+        <v>0.1</v>
+      </c>
+      <c r="F145">
+        <v>4</v>
+      </c>
+      <c r="G145">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="D146">
+        <v>0.3</v>
+      </c>
+      <c r="E146">
+        <v>0.2</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>14</v>
+      </c>
+      <c r="C147">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="D147">
+        <v>0.3</v>
+      </c>
+      <c r="E147">
+        <v>0.2</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>14</v>
+      </c>
+      <c r="C148">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="D148">
+        <v>0.3</v>
+      </c>
+      <c r="E148">
+        <v>0.2</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>14</v>
+      </c>
+      <c r="C149">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="D149">
+        <v>0.3</v>
+      </c>
+      <c r="E149">
+        <v>0.2</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150">
+        <v>138.30000000000001</v>
+      </c>
+      <c r="D150">
+        <v>0.3</v>
+      </c>
+      <c r="E150">
+        <v>0.2</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+      <c r="G150">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151">
+        <v>155.1</v>
+      </c>
+      <c r="D151">
+        <v>0.3</v>
+      </c>
+      <c r="E151">
+        <v>0.2</v>
+      </c>
+      <c r="F151">
+        <v>2</v>
+      </c>
+      <c r="G151">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152">
+        <v>144.80000000000001</v>
+      </c>
+      <c r="D152">
+        <v>0.3</v>
+      </c>
+      <c r="E152">
+        <v>0.2</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+      <c r="G152">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D153">
+        <v>0.3</v>
+      </c>
+      <c r="E153">
+        <v>0.2</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="D154">
+        <v>0.3</v>
+      </c>
+      <c r="E154">
+        <v>0.2</v>
+      </c>
+      <c r="F154">
+        <v>3</v>
+      </c>
+      <c r="G154">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>14</v>
+      </c>
+      <c r="C155">
+        <v>157.5</v>
+      </c>
+      <c r="D155">
+        <v>0.3</v>
+      </c>
+      <c r="E155">
+        <v>0.2</v>
+      </c>
+      <c r="F155">
+        <v>3</v>
+      </c>
+      <c r="G155">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>14</v>
+      </c>
+      <c r="C156">
+        <v>123.3</v>
+      </c>
+      <c r="D156">
+        <v>0.3</v>
+      </c>
+      <c r="E156">
+        <v>0.2</v>
+      </c>
+      <c r="F156">
+        <v>3</v>
+      </c>
+      <c r="G156">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>14</v>
+      </c>
+      <c r="C157">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="D157">
+        <v>0.3</v>
+      </c>
+      <c r="E157">
+        <v>0.2</v>
+      </c>
+      <c r="F157">
+        <v>3</v>
+      </c>
+      <c r="G157">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>14</v>
+      </c>
+      <c r="C158">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="D158">
+        <v>0.3</v>
+      </c>
+      <c r="E158">
+        <v>0.2</v>
+      </c>
+      <c r="F158">
+        <v>4</v>
+      </c>
+      <c r="G158">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>14</v>
+      </c>
+      <c r="C159">
+        <v>149.6</v>
+      </c>
+      <c r="D159">
+        <v>0.3</v>
+      </c>
+      <c r="E159">
+        <v>0.2</v>
+      </c>
+      <c r="F159">
+        <v>4</v>
+      </c>
+      <c r="G159">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>14</v>
+      </c>
+      <c r="C160">
+        <v>148.5</v>
+      </c>
+      <c r="D160">
+        <v>0.3</v>
+      </c>
+      <c r="E160">
+        <v>0.2</v>
+      </c>
+      <c r="F160">
+        <v>4</v>
+      </c>
+      <c r="G160">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="D161">
+        <v>0.3</v>
+      </c>
+      <c r="E161">
+        <v>0.2</v>
+      </c>
+      <c r="F161">
+        <v>4</v>
+      </c>
+      <c r="G161">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162">
+        <v>142.5</v>
+      </c>
+      <c r="D162">
+        <v>0.3</v>
+      </c>
+      <c r="E162">
+        <v>0.3</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163">
+        <v>141.5</v>
+      </c>
+      <c r="D163">
+        <v>0.3</v>
+      </c>
+      <c r="E163">
+        <v>0.3</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="D164">
+        <v>0.3</v>
+      </c>
+      <c r="E164">
+        <v>0.3</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>14</v>
+      </c>
+      <c r="C165">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="D165">
+        <v>0.3</v>
+      </c>
+      <c r="E165">
+        <v>0.3</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>14</v>
+      </c>
+      <c r="C166">
+        <v>151.6</v>
+      </c>
+      <c r="D166">
+        <v>0.3</v>
+      </c>
+      <c r="E166">
+        <v>0.3</v>
+      </c>
+      <c r="F166">
+        <v>2</v>
+      </c>
+      <c r="G166">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>14</v>
+      </c>
+      <c r="C167">
+        <v>146.1</v>
+      </c>
+      <c r="D167">
+        <v>0.3</v>
+      </c>
+      <c r="E167">
+        <v>0.3</v>
+      </c>
+      <c r="F167">
+        <v>2</v>
+      </c>
+      <c r="G167">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D168">
+        <v>0.3</v>
+      </c>
+      <c r="E168">
+        <v>0.3</v>
+      </c>
+      <c r="F168">
+        <v>2</v>
+      </c>
+      <c r="G168">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="D169">
+        <v>0.3</v>
+      </c>
+      <c r="E169">
+        <v>0.3</v>
+      </c>
+      <c r="F169">
+        <v>2</v>
+      </c>
+      <c r="G169">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170">
+        <v>162</v>
+      </c>
+      <c r="D170">
+        <v>0.3</v>
+      </c>
+      <c r="E170">
+        <v>0.3</v>
+      </c>
+      <c r="F170">
+        <v>3</v>
+      </c>
+      <c r="G170">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>14</v>
+      </c>
+      <c r="C171">
+        <v>148</v>
+      </c>
+      <c r="D171">
+        <v>0.3</v>
+      </c>
+      <c r="E171">
+        <v>0.3</v>
+      </c>
+      <c r="F171">
+        <v>3</v>
+      </c>
+      <c r="G171">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>14</v>
+      </c>
+      <c r="C172">
+        <v>146</v>
+      </c>
+      <c r="D172">
+        <v>0.3</v>
+      </c>
+      <c r="E172">
+        <v>0.3</v>
+      </c>
+      <c r="F172">
+        <v>3</v>
+      </c>
+      <c r="G172">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173">
+        <v>138.30000000000001</v>
+      </c>
+      <c r="D173">
+        <v>0.3</v>
+      </c>
+      <c r="E173">
+        <v>0.3</v>
+      </c>
+      <c r="F173">
+        <v>3</v>
+      </c>
+      <c r="G173">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174">
+        <v>147</v>
+      </c>
+      <c r="D174">
+        <v>0.3</v>
+      </c>
+      <c r="E174">
+        <v>0.3</v>
+      </c>
+      <c r="F174">
+        <v>4</v>
+      </c>
+      <c r="G174">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>14</v>
+      </c>
+      <c r="C175">
+        <v>144.30000000000001</v>
+      </c>
+      <c r="D175">
+        <v>0.3</v>
+      </c>
+      <c r="E175">
+        <v>0.3</v>
+      </c>
+      <c r="F175">
+        <v>4</v>
+      </c>
+      <c r="G175">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>14</v>
+      </c>
+      <c r="C176">
+        <v>150.9</v>
+      </c>
+      <c r="D176">
+        <v>0.3</v>
+      </c>
+      <c r="E176">
+        <v>0.3</v>
+      </c>
+      <c r="F176">
+        <v>4</v>
+      </c>
+      <c r="G176">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>14</v>
+      </c>
+      <c r="C177">
+        <v>130.9</v>
+      </c>
+      <c r="D177">
+        <v>0.3</v>
+      </c>
+      <c r="E177">
+        <v>0.3</v>
+      </c>
+      <c r="F177">
+        <v>4</v>
+      </c>
+      <c r="G177">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="D178">
+        <v>0.3</v>
+      </c>
+      <c r="E178">
+        <v>0.4</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179">
+        <v>166.8</v>
+      </c>
+      <c r="D179">
+        <v>0.3</v>
+      </c>
+      <c r="E179">
+        <v>0.4</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="D180">
+        <v>0.3</v>
+      </c>
+      <c r="E180">
+        <v>0.4</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181">
+        <v>135.69999999999999</v>
+      </c>
+      <c r="D181">
+        <v>0.3</v>
+      </c>
+      <c r="E181">
+        <v>0.4</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="D182">
+        <v>0.3</v>
+      </c>
+      <c r="E182">
+        <v>0.4</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>14</v>
+      </c>
+      <c r="C183">
+        <v>162</v>
+      </c>
+      <c r="D183">
+        <v>0.3</v>
+      </c>
+      <c r="E183">
+        <v>0.4</v>
+      </c>
+      <c r="F183">
+        <v>2</v>
+      </c>
+      <c r="G183">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184">
+        <v>144</v>
+      </c>
+      <c r="D184">
+        <v>0.3</v>
+      </c>
+      <c r="E184">
+        <v>0.4</v>
+      </c>
+      <c r="F184">
+        <v>2</v>
+      </c>
+      <c r="G184">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D185">
+        <v>0.3</v>
+      </c>
+      <c r="E185">
+        <v>0.4</v>
+      </c>
+      <c r="F185">
+        <v>2</v>
+      </c>
+      <c r="G185">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>14</v>
+      </c>
+      <c r="C186">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="D186">
+        <v>0.3</v>
+      </c>
+      <c r="E186">
+        <v>0.4</v>
+      </c>
+      <c r="F186">
+        <v>3</v>
+      </c>
+      <c r="G186">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>14</v>
+      </c>
+      <c r="C187">
+        <v>137.1</v>
+      </c>
+      <c r="D187">
+        <v>0.3</v>
+      </c>
+      <c r="E187">
+        <v>0.4</v>
+      </c>
+      <c r="F187">
+        <v>3</v>
+      </c>
+      <c r="G187">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188">
+        <v>142.6</v>
+      </c>
+      <c r="D188">
+        <v>0.3</v>
+      </c>
+      <c r="E188">
+        <v>0.4</v>
+      </c>
+      <c r="F188">
+        <v>3</v>
+      </c>
+      <c r="G188">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>14</v>
+      </c>
+      <c r="C189">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="D189">
+        <v>0.3</v>
+      </c>
+      <c r="E189">
+        <v>0.4</v>
+      </c>
+      <c r="F189">
+        <v>3</v>
+      </c>
+      <c r="G189">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>14</v>
+      </c>
+      <c r="C190">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="D190">
+        <v>0.3</v>
+      </c>
+      <c r="E190">
+        <v>0.4</v>
+      </c>
+      <c r="F190">
+        <v>4</v>
+      </c>
+      <c r="G190">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>14</v>
+      </c>
+      <c r="C191">
+        <v>117.8</v>
+      </c>
+      <c r="D191">
+        <v>0.3</v>
+      </c>
+      <c r="E191">
+        <v>0.4</v>
+      </c>
+      <c r="F191">
+        <v>4</v>
+      </c>
+      <c r="G191">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>14</v>
+      </c>
+      <c r="C192">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="D192">
+        <v>0.3</v>
+      </c>
+      <c r="E192">
+        <v>0.4</v>
+      </c>
+      <c r="F192">
+        <v>4</v>
+      </c>
+      <c r="G192">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>14</v>
+      </c>
+      <c r="C193">
+        <v>141</v>
+      </c>
+      <c r="D193">
+        <v>0.3</v>
+      </c>
+      <c r="E193">
+        <v>0.4</v>
+      </c>
+      <c r="F193">
+        <v>4</v>
+      </c>
+      <c r="G193">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194">
+        <v>144.5</v>
+      </c>
+      <c r="D194">
+        <v>0.4</v>
+      </c>
+      <c r="E194">
+        <v>0.1</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C195">
+        <v>151.1</v>
+      </c>
+      <c r="D195">
+        <v>0.4</v>
+      </c>
+      <c r="E195">
+        <v>0.1</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="D196">
+        <v>0.4</v>
+      </c>
+      <c r="E196">
+        <v>0.1</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197">
+        <v>156.1</v>
+      </c>
+      <c r="D197">
+        <v>0.4</v>
+      </c>
+      <c r="E197">
+        <v>0.1</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="D198">
+        <v>0.4</v>
+      </c>
+      <c r="E198">
+        <v>0.1</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="D199">
+        <v>0.4</v>
+      </c>
+      <c r="E199">
+        <v>0.1</v>
+      </c>
+      <c r="F199">
+        <v>2</v>
+      </c>
+      <c r="G199">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200">
+        <v>165.5</v>
+      </c>
+      <c r="D200">
+        <v>0.4</v>
+      </c>
+      <c r="E200">
+        <v>0.1</v>
+      </c>
+      <c r="F200">
+        <v>2</v>
+      </c>
+      <c r="G200">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201">
+        <v>146</v>
+      </c>
+      <c r="D201">
+        <v>0.4</v>
+      </c>
+      <c r="E201">
+        <v>0.1</v>
+      </c>
+      <c r="F201">
+        <v>2</v>
+      </c>
+      <c r="G201">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D202">
+        <v>0.4</v>
+      </c>
+      <c r="E202">
+        <v>0.1</v>
+      </c>
+      <c r="F202">
+        <v>3</v>
+      </c>
+      <c r="G202">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203">
+        <v>170.6</v>
+      </c>
+      <c r="D203">
+        <v>0.4</v>
+      </c>
+      <c r="E203">
+        <v>0.1</v>
+      </c>
+      <c r="F203">
+        <v>3</v>
+      </c>
+      <c r="G203">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204">
+        <v>135.5</v>
+      </c>
+      <c r="D204">
+        <v>0.4</v>
+      </c>
+      <c r="E204">
+        <v>0.1</v>
+      </c>
+      <c r="F204">
+        <v>3</v>
+      </c>
+      <c r="G204">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="D205">
+        <v>0.4</v>
+      </c>
+      <c r="E205">
+        <v>0.1</v>
+      </c>
+      <c r="F205">
+        <v>3</v>
+      </c>
+      <c r="G205">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="D206">
+        <v>0.4</v>
+      </c>
+      <c r="E206">
+        <v>0.1</v>
+      </c>
+      <c r="F206">
+        <v>4</v>
+      </c>
+      <c r="G206">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207">
+        <v>118.8</v>
+      </c>
+      <c r="D207">
+        <v>0.4</v>
+      </c>
+      <c r="E207">
+        <v>0.1</v>
+      </c>
+      <c r="F207">
+        <v>4</v>
+      </c>
+      <c r="G207">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>14</v>
+      </c>
+      <c r="C208">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="D208">
+        <v>0.4</v>
+      </c>
+      <c r="E208">
+        <v>0.1</v>
+      </c>
+      <c r="F208">
+        <v>4</v>
+      </c>
+      <c r="G208">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>14</v>
+      </c>
+      <c r="C209">
+        <v>120.1</v>
+      </c>
+      <c r="D209">
+        <v>0.4</v>
+      </c>
+      <c r="E209">
+        <v>0.1</v>
+      </c>
+      <c r="F209">
+        <v>4</v>
+      </c>
+      <c r="G209">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210">
+        <v>143.5</v>
+      </c>
+      <c r="D210">
+        <v>0.4</v>
+      </c>
+      <c r="E210">
+        <v>0.2</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211">
+        <v>155.1</v>
+      </c>
+      <c r="D211">
+        <v>0.4</v>
+      </c>
+      <c r="E211">
+        <v>0.2</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="D212">
+        <v>0.4</v>
+      </c>
+      <c r="E212">
+        <v>0.2</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213">
+        <v>141.1</v>
+      </c>
+      <c r="D213">
+        <v>0.4</v>
+      </c>
+      <c r="E213">
+        <v>0.2</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="D214">
+        <v>0.4</v>
+      </c>
+      <c r="E214">
+        <v>0.2</v>
+      </c>
+      <c r="F214">
+        <v>2</v>
+      </c>
+      <c r="G214">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215">
+        <v>147.6</v>
+      </c>
+      <c r="D215">
+        <v>0.4</v>
+      </c>
+      <c r="E215">
+        <v>0.2</v>
+      </c>
+      <c r="F215">
+        <v>2</v>
+      </c>
+      <c r="G215">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="D216">
+        <v>0.4</v>
+      </c>
+      <c r="E216">
+        <v>0.2</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217">
+        <v>147</v>
+      </c>
+      <c r="D217">
+        <v>0.4</v>
+      </c>
+      <c r="E217">
+        <v>0.2</v>
+      </c>
+      <c r="F217">
+        <v>2</v>
+      </c>
+      <c r="G217">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="D218">
+        <v>0.4</v>
+      </c>
+      <c r="E218">
+        <v>0.2</v>
+      </c>
+      <c r="F218">
+        <v>3</v>
+      </c>
+      <c r="G218">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>14</v>
+      </c>
+      <c r="C219">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="D219">
+        <v>0.4</v>
+      </c>
+      <c r="E219">
+        <v>0.2</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
+      </c>
+      <c r="G219">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220">
+        <v>148.1</v>
+      </c>
+      <c r="D220">
+        <v>0.4</v>
+      </c>
+      <c r="E220">
+        <v>0.2</v>
+      </c>
+      <c r="F220">
+        <v>3</v>
+      </c>
+      <c r="G220">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221">
+        <v>144</v>
+      </c>
+      <c r="D221">
+        <v>0.4</v>
+      </c>
+      <c r="E221">
+        <v>0.2</v>
+      </c>
+      <c r="F221">
+        <v>3</v>
+      </c>
+      <c r="G221">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222">
+        <v>144.6</v>
+      </c>
+      <c r="D222">
+        <v>0.4</v>
+      </c>
+      <c r="E222">
+        <v>0.2</v>
+      </c>
+      <c r="F222">
+        <v>4</v>
+      </c>
+      <c r="G222">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="D223">
+        <v>0.4</v>
+      </c>
+      <c r="E223">
+        <v>0.2</v>
+      </c>
+      <c r="F223">
+        <v>4</v>
+      </c>
+      <c r="G223">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224">
+        <v>156.5</v>
+      </c>
+      <c r="D224">
+        <v>0.4</v>
+      </c>
+      <c r="E224">
+        <v>0.2</v>
+      </c>
+      <c r="F224">
+        <v>4</v>
+      </c>
+      <c r="G224">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>14</v>
+      </c>
+      <c r="C225">
+        <v>130</v>
+      </c>
+      <c r="D225">
+        <v>0.4</v>
+      </c>
+      <c r="E225">
+        <v>0.2</v>
+      </c>
+      <c r="F225">
+        <v>4</v>
+      </c>
+      <c r="G225">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="D226">
+        <v>0.4</v>
+      </c>
+      <c r="E226">
+        <v>0.3</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="D227">
+        <v>0.4</v>
+      </c>
+      <c r="E227">
+        <v>0.3</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="D228">
+        <v>0.4</v>
+      </c>
+      <c r="E228">
+        <v>0.3</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229">
+        <v>143</v>
+      </c>
+      <c r="D229">
+        <v>0.4</v>
+      </c>
+      <c r="E229">
+        <v>0.3</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>14</v>
+      </c>
+      <c r="C230">
+        <v>144.80000000000001</v>
+      </c>
+      <c r="D230">
+        <v>0.4</v>
+      </c>
+      <c r="E230">
+        <v>0.3</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+      <c r="G230">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>14</v>
+      </c>
+      <c r="C231">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D231">
+        <v>0.4</v>
+      </c>
+      <c r="E231">
+        <v>0.3</v>
+      </c>
+      <c r="F231">
+        <v>2</v>
+      </c>
+      <c r="G231">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232">
+        <v>147.1</v>
+      </c>
+      <c r="D232">
+        <v>0.4</v>
+      </c>
+      <c r="E232">
+        <v>0.3</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233">
+        <v>145.6</v>
+      </c>
+      <c r="D233">
+        <v>0.4</v>
+      </c>
+      <c r="E233">
+        <v>0.3</v>
+      </c>
+      <c r="F233">
+        <v>2</v>
+      </c>
+      <c r="G233">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="D234">
+        <v>0.4</v>
+      </c>
+      <c r="E234">
+        <v>0.3</v>
+      </c>
+      <c r="F234">
+        <v>3</v>
+      </c>
+      <c r="G234">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235">
+        <v>143</v>
+      </c>
+      <c r="D235">
+        <v>0.4</v>
+      </c>
+      <c r="E235">
+        <v>0.3</v>
+      </c>
+      <c r="F235">
+        <v>3</v>
+      </c>
+      <c r="G235">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236">
+        <v>148.6</v>
+      </c>
+      <c r="D236">
+        <v>0.4</v>
+      </c>
+      <c r="E236">
+        <v>0.3</v>
+      </c>
+      <c r="F236">
+        <v>3</v>
+      </c>
+      <c r="G236">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237">
+        <v>153</v>
+      </c>
+      <c r="D237">
+        <v>0.4</v>
+      </c>
+      <c r="E237">
+        <v>0.3</v>
+      </c>
+      <c r="F237">
+        <v>3</v>
+      </c>
+      <c r="G237">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="D238">
+        <v>0.4</v>
+      </c>
+      <c r="E238">
+        <v>0.3</v>
+      </c>
+      <c r="F238">
+        <v>4</v>
+      </c>
+      <c r="G238">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="D239">
+        <v>0.4</v>
+      </c>
+      <c r="E239">
+        <v>0.3</v>
+      </c>
+      <c r="F239">
+        <v>4</v>
+      </c>
+      <c r="G239">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240">
+        <v>151.1</v>
+      </c>
+      <c r="D240">
+        <v>0.4</v>
+      </c>
+      <c r="E240">
+        <v>0.3</v>
+      </c>
+      <c r="F240">
+        <v>4</v>
+      </c>
+      <c r="G240">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241">
+        <v>144</v>
+      </c>
+      <c r="D241">
+        <v>0.4</v>
+      </c>
+      <c r="E241">
+        <v>0.3</v>
+      </c>
+      <c r="F241">
+        <v>4</v>
+      </c>
+      <c r="G241">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D242">
+        <v>0.4</v>
+      </c>
+      <c r="E242">
+        <v>0.4</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243">
+        <v>149.6</v>
+      </c>
+      <c r="D243">
+        <v>0.4</v>
+      </c>
+      <c r="E243">
+        <v>0.4</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+      <c r="G243">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="D244">
+        <v>0.4</v>
+      </c>
+      <c r="E244">
+        <v>0.4</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>14</v>
+      </c>
+      <c r="C245">
+        <v>138</v>
+      </c>
+      <c r="D245">
+        <v>0.4</v>
+      </c>
+      <c r="E245">
+        <v>0.4</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246">
+        <v>129.1</v>
+      </c>
+      <c r="D246">
+        <v>0.4</v>
+      </c>
+      <c r="E246">
+        <v>0.4</v>
+      </c>
+      <c r="F246">
+        <v>2</v>
+      </c>
+      <c r="G246">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247">
+        <v>159.1</v>
+      </c>
+      <c r="D247">
+        <v>0.4</v>
+      </c>
+      <c r="E247">
+        <v>0.4</v>
+      </c>
+      <c r="F247">
+        <v>2</v>
+      </c>
+      <c r="G247">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>14</v>
+      </c>
+      <c r="C248">
+        <v>151.5</v>
+      </c>
+      <c r="D248">
+        <v>0.4</v>
+      </c>
+      <c r="E248">
+        <v>0.4</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+      <c r="G248">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249">
+        <v>147.1</v>
+      </c>
+      <c r="D249">
+        <v>0.4</v>
+      </c>
+      <c r="E249">
+        <v>0.4</v>
+      </c>
+      <c r="F249">
+        <v>2</v>
+      </c>
+      <c r="G249">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250">
+        <v>140.1</v>
+      </c>
+      <c r="D250">
+        <v>0.4</v>
+      </c>
+      <c r="E250">
+        <v>0.4</v>
+      </c>
+      <c r="F250">
+        <v>3</v>
+      </c>
+      <c r="G250">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>14</v>
+      </c>
+      <c r="C251">
+        <v>148.1</v>
+      </c>
+      <c r="D251">
+        <v>0.4</v>
+      </c>
+      <c r="E251">
+        <v>0.4</v>
+      </c>
+      <c r="F251">
+        <v>3</v>
+      </c>
+      <c r="G251">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="D252">
+        <v>0.4</v>
+      </c>
+      <c r="E252">
+        <v>0.4</v>
+      </c>
+      <c r="F252">
+        <v>3</v>
+      </c>
+      <c r="G252">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253">
+        <v>147</v>
+      </c>
+      <c r="D253">
+        <v>0.4</v>
+      </c>
+      <c r="E253">
+        <v>0.4</v>
+      </c>
+      <c r="F253">
+        <v>3</v>
+      </c>
+      <c r="G253">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="D254">
+        <v>0.4</v>
+      </c>
+      <c r="E254">
+        <v>0.4</v>
+      </c>
+      <c r="F254">
+        <v>4</v>
+      </c>
+      <c r="G254">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255">
+        <v>147.4</v>
+      </c>
+      <c r="D255">
+        <v>0.4</v>
+      </c>
+      <c r="E255">
+        <v>0.4</v>
+      </c>
+      <c r="F255">
+        <v>4</v>
+      </c>
+      <c r="G255">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="D256">
+        <v>0.4</v>
+      </c>
+      <c r="E256">
+        <v>0.4</v>
+      </c>
+      <c r="F256">
+        <v>4</v>
+      </c>
+      <c r="G256">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="D257">
+        <v>0.4</v>
+      </c>
+      <c r="E257">
+        <v>0.4</v>
+      </c>
+      <c r="F257">
+        <v>4</v>
+      </c>
+      <c r="G257">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C258">
+        <f>MIN(C2:C257)</f>
+        <v>93.799999999999983</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>